--- a/IPL Player.xlsx
+++ b/IPL Player.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vishwesh/Documents/WPL&amp;BBL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94F7FDC-2916-0A42-9165-05AE4C7FB749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F8AF69-A22C-4546-9C64-86D45006C8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{D0DA0628-277F-DE4B-AFF3-EE6AAC7B380B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5282" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5287" uniqueCount="782">
   <si>
     <t>Team Name</t>
   </si>
@@ -2382,6 +2382,9 @@
   </si>
   <si>
     <t>Kusal Mendis</t>
+  </si>
+  <si>
+    <t>George Linde</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2784,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC219B49-20BB-ED4C-B167-301B561CF408}">
-  <dimension ref="A1:F1084"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F1085"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -2812,7 +2816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>146</v>
       </c>
@@ -2832,7 +2836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>56</v>
       </c>
@@ -2852,7 +2856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2872,7 +2876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>712</v>
       </c>
@@ -2912,7 +2916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>712</v>
       </c>
@@ -2932,7 +2936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -2972,7 +2976,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>172</v>
       </c>
@@ -2992,7 +2996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -3008,7 +3012,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>146</v>
       </c>
@@ -3028,7 +3032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>146</v>
       </c>
@@ -3048,7 +3052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>172</v>
       </c>
@@ -3068,7 +3072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>146</v>
       </c>
@@ -3088,7 +3092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>263</v>
       </c>
@@ -3108,7 +3112,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>172</v>
       </c>
@@ -3128,7 +3132,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>172</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>505</v>
       </c>
@@ -3168,7 +3172,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>146</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -3208,7 +3212,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>222</v>
       </c>
@@ -3228,7 +3232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -3248,7 +3252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>172</v>
       </c>
@@ -3268,7 +3272,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
@@ -3286,7 +3290,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>146</v>
       </c>
@@ -3306,7 +3310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>222</v>
       </c>
@@ -3326,7 +3330,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>146</v>
       </c>
@@ -3346,7 +3350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>222</v>
       </c>
@@ -3366,7 +3370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>146</v>
       </c>
@@ -3386,7 +3390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -3406,7 +3410,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>172</v>
       </c>
@@ -3426,7 +3430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>172</v>
       </c>
@@ -3446,7 +3450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>172</v>
       </c>
@@ -3466,7 +3470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -3484,7 +3488,7 @@
       </c>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -3504,7 +3508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>222</v>
       </c>
@@ -3522,7 +3526,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>172</v>
       </c>
@@ -3540,7 +3544,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>222</v>
       </c>
@@ -3580,7 +3584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>172</v>
       </c>
@@ -3600,7 +3604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -3620,7 +3624,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>111</v>
       </c>
@@ -3640,7 +3644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>111</v>
       </c>
@@ -3660,7 +3664,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,7 +3684,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>222</v>
       </c>
@@ -3700,7 +3704,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -3720,7 +3724,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -3740,7 +3744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
@@ -3780,7 +3784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>146</v>
       </c>
@@ -3800,7 +3804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -3840,7 +3844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>172</v>
       </c>
@@ -3860,7 +3864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>505</v>
       </c>
@@ -3880,7 +3884,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>222</v>
       </c>
@@ -3900,7 +3904,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>172</v>
       </c>
@@ -3920,7 +3924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>146</v>
       </c>
@@ -3940,7 +3944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>222</v>
       </c>
@@ -3960,7 +3964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>505</v>
       </c>
@@ -3980,7 +3984,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>172</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>222</v>
       </c>
@@ -4020,7 +4024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>263</v>
       </c>
@@ -4040,7 +4044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>222</v>
       </c>
@@ -4060,7 +4064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>146</v>
       </c>
@@ -4080,7 +4084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>111</v>
       </c>
@@ -4100,7 +4104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>505</v>
       </c>
@@ -4120,7 +4124,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>222</v>
       </c>
@@ -4140,7 +4144,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>111</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>172</v>
       </c>
@@ -4200,7 +4204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -4218,7 +4222,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -4238,7 +4242,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -4256,7 +4260,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>222</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>172</v>
       </c>
@@ -4296,7 +4300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>222</v>
       </c>
@@ -4316,7 +4320,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>56</v>
       </c>
@@ -4336,7 +4340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>505</v>
       </c>
@@ -4356,7 +4360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>146</v>
       </c>
@@ -4376,7 +4380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>222</v>
       </c>
@@ -4396,7 +4400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>146</v>
       </c>
@@ -4416,7 +4420,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>56</v>
       </c>
@@ -4436,7 +4440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>56</v>
       </c>
@@ -4456,7 +4460,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>146</v>
       </c>
@@ -4476,7 +4480,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>172</v>
       </c>
@@ -4496,7 +4500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>172</v>
       </c>
@@ -4516,7 +4520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>146</v>
       </c>
@@ -4536,7 +4540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>146</v>
       </c>
@@ -4556,7 +4560,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>222</v>
       </c>
@@ -4576,7 +4580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -4596,7 +4600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>505</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>56</v>
       </c>
@@ -4636,7 +4640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -4656,7 +4660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>172</v>
       </c>
@@ -4676,7 +4680,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>111</v>
       </c>
@@ -4694,7 +4698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>222</v>
       </c>
@@ -4714,7 +4718,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>172</v>
       </c>
@@ -4734,7 +4738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>111</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>56</v>
       </c>
@@ -4774,7 +4778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>505</v>
       </c>
@@ -4794,7 +4798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>263</v>
       </c>
@@ -4812,7 +4816,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>146</v>
       </c>
@@ -4830,7 +4834,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>56</v>
       </c>
@@ -4850,7 +4854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>222</v>
       </c>
@@ -4870,7 +4874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -4888,7 +4892,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>56</v>
       </c>
@@ -4908,7 +4912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>56</v>
       </c>
@@ -4948,7 +4952,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>222</v>
       </c>
@@ -4968,7 +4972,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>56</v>
       </c>
@@ -4988,7 +4992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
@@ -5028,7 +5032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>263</v>
       </c>
@@ -5048,7 +5052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>712</v>
       </c>
@@ -5068,7 +5072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>712</v>
       </c>
@@ -5108,7 +5112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>505</v>
       </c>
@@ -5128,7 +5132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>146</v>
       </c>
@@ -5148,7 +5152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -5186,7 +5190,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>146</v>
       </c>
@@ -5206,7 +5210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>222</v>
       </c>
@@ -5226,7 +5230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>222</v>
       </c>
@@ -5246,7 +5250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>172</v>
       </c>
@@ -5266,7 +5270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>172</v>
       </c>
@@ -5286,7 +5290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>146</v>
       </c>
@@ -5306,7 +5310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>56</v>
       </c>
@@ -5326,7 +5330,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -5346,7 +5350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>6</v>
       </c>
@@ -5366,7 +5370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>6</v>
       </c>
@@ -5384,7 +5388,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>111</v>
       </c>
@@ -5402,7 +5406,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>222</v>
       </c>
@@ -5422,7 +5426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>222</v>
       </c>
@@ -5442,7 +5446,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>111</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>172</v>
       </c>
@@ -5482,7 +5486,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>172</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>6</v>
       </c>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>111</v>
       </c>
@@ -5560,7 +5564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>146</v>
       </c>
@@ -5580,7 +5584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>146</v>
       </c>
@@ -5600,7 +5604,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>111</v>
       </c>
@@ -5620,7 +5624,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>222</v>
       </c>
@@ -5660,7 +5664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>505</v>
       </c>
@@ -5680,7 +5684,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>263</v>
       </c>
@@ -5700,7 +5704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>712</v>
       </c>
@@ -5720,7 +5724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>712</v>
       </c>
@@ -5740,7 +5744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>505</v>
       </c>
@@ -5760,7 +5764,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>146</v>
       </c>
@@ -5780,7 +5784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>111</v>
       </c>
@@ -5800,7 +5804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>222</v>
       </c>
@@ -5820,7 +5824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>172</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>172</v>
       </c>
@@ -5860,7 +5864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>222</v>
       </c>
@@ -5880,7 +5884,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>172</v>
       </c>
@@ -5900,7 +5904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>111</v>
       </c>
@@ -5920,7 +5924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>505</v>
       </c>
@@ -5940,7 +5944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>505</v>
       </c>
@@ -5960,7 +5964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>6</v>
       </c>
@@ -5980,7 +5984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>172</v>
       </c>
@@ -6000,7 +6004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>6</v>
       </c>
@@ -6020,7 +6024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>222</v>
       </c>
@@ -6040,7 +6044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>222</v>
       </c>
@@ -6060,7 +6064,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>146</v>
       </c>
@@ -6080,7 +6084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>146</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>172</v>
       </c>
@@ -6120,7 +6124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>146</v>
       </c>
@@ -6140,7 +6144,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>172</v>
       </c>
@@ -6160,7 +6164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -6180,7 +6184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
@@ -6200,7 +6204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>146</v>
       </c>
@@ -6220,7 +6224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>146</v>
       </c>
@@ -6240,7 +6244,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>263</v>
       </c>
@@ -6258,7 +6262,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>56</v>
       </c>
@@ -6276,7 +6280,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>56</v>
       </c>
@@ -6296,7 +6300,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>6</v>
       </c>
@@ -6316,7 +6320,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>56</v>
       </c>
@@ -6336,7 +6340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -6356,7 +6360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>56</v>
       </c>
@@ -6376,7 +6380,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>146</v>
       </c>
@@ -6396,7 +6400,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>56</v>
       </c>
@@ -6416,7 +6420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>505</v>
       </c>
@@ -6434,7 +6438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>56</v>
       </c>
@@ -6454,7 +6458,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>146</v>
       </c>
@@ -6474,7 +6478,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>146</v>
       </c>
@@ -6494,7 +6498,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>172</v>
       </c>
@@ -6514,7 +6518,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>172</v>
       </c>
@@ -6534,7 +6538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>505</v>
       </c>
@@ -6554,7 +6558,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>146</v>
       </c>
@@ -6574,7 +6578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>172</v>
       </c>
@@ -6594,7 +6598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>505</v>
       </c>
@@ -6614,7 +6618,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>222</v>
       </c>
@@ -6632,7 +6636,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>505</v>
       </c>
@@ -6650,7 +6654,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>222</v>
       </c>
@@ -6670,7 +6674,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,7 +6694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>146</v>
       </c>
@@ -6710,7 +6714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>111</v>
       </c>
@@ -6730,7 +6734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>56</v>
       </c>
@@ -6750,7 +6754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>222</v>
       </c>
@@ -6768,7 +6772,7 @@
       </c>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>56</v>
       </c>
@@ -6788,7 +6792,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>146</v>
       </c>
@@ -6808,7 +6812,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>146</v>
       </c>
@@ -6826,7 +6830,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>56</v>
       </c>
@@ -6846,7 +6850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>56</v>
       </c>
@@ -6862,7 +6866,7 @@
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>146</v>
       </c>
@@ -6882,7 +6886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>56</v>
       </c>
@@ -6902,7 +6906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>146</v>
       </c>
@@ -6922,7 +6926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>146</v>
       </c>
@@ -6942,7 +6946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>172</v>
       </c>
@@ -6962,7 +6966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>56</v>
       </c>
@@ -6982,7 +6986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>172</v>
       </c>
@@ -7002,7 +7006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>505</v>
       </c>
@@ -7022,7 +7026,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>111</v>
       </c>
@@ -7042,7 +7046,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>56</v>
       </c>
@@ -7062,7 +7066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>146</v>
       </c>
@@ -7082,7 +7086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>222</v>
       </c>
@@ -7102,7 +7106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>172</v>
       </c>
@@ -7122,7 +7126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>56</v>
       </c>
@@ -7142,7 +7146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>146</v>
       </c>
@@ -7162,7 +7166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>111</v>
       </c>
@@ -7182,7 +7186,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>111</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>56</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>222</v>
       </c>
@@ -7242,7 +7246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>222</v>
       </c>
@@ -7262,7 +7266,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>146</v>
       </c>
@@ -7282,7 +7286,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>6</v>
       </c>
@@ -7302,7 +7306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>146</v>
       </c>
@@ -7322,7 +7326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>172</v>
       </c>
@@ -7342,7 +7346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>6</v>
       </c>
@@ -7362,7 +7366,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>146</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>146</v>
       </c>
@@ -7422,7 +7426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>146</v>
       </c>
@@ -7442,7 +7446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>172</v>
       </c>
@@ -7462,7 +7466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>56</v>
       </c>
@@ -7482,7 +7486,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>6</v>
       </c>
@@ -7502,7 +7506,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>111</v>
       </c>
@@ -7522,7 +7526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>263</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>263</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>56</v>
       </c>
@@ -7582,7 +7586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>263</v>
       </c>
@@ -7622,7 +7626,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>111</v>
       </c>
@@ -7642,7 +7646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>172</v>
       </c>
@@ -7662,7 +7666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>146</v>
       </c>
@@ -7682,7 +7686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>505</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>146</v>
       </c>
@@ -7722,7 +7726,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>222</v>
       </c>
@@ -7742,7 +7746,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>56</v>
       </c>
@@ -7762,7 +7766,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>505</v>
       </c>
@@ -7782,7 +7786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>222</v>
       </c>
@@ -7802,7 +7806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>6</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
         <v>505</v>
       </c>
@@ -7862,7 +7866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
         <v>172</v>
       </c>
@@ -7882,7 +7886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
         <v>222</v>
       </c>
@@ -7902,7 +7906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
         <v>146</v>
       </c>
@@ -7922,7 +7926,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>505</v>
       </c>
@@ -7942,7 +7946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
         <v>146</v>
       </c>
@@ -7958,7 +7962,7 @@
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>505</v>
       </c>
@@ -7978,7 +7982,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>222</v>
       </c>
@@ -7998,7 +8002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>6</v>
       </c>
@@ -8018,7 +8022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>6</v>
       </c>
@@ -8036,7 +8040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
         <v>505</v>
       </c>
@@ -8076,7 +8080,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
         <v>222</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>146</v>
       </c>
@@ -8114,7 +8118,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
         <v>6</v>
       </c>
@@ -8134,7 +8138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
         <v>6</v>
       </c>
@@ -8154,7 +8158,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>56</v>
       </c>
@@ -8174,7 +8178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
         <v>222</v>
       </c>
@@ -8194,7 +8198,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
         <v>146</v>
       </c>
@@ -8214,7 +8218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
         <v>6</v>
       </c>
@@ -8234,7 +8238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>505</v>
       </c>
@@ -8254,7 +8258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
         <v>146</v>
       </c>
@@ -8274,7 +8278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
         <v>6</v>
       </c>
@@ -8292,7 +8296,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
         <v>263</v>
       </c>
@@ -8312,7 +8316,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>222</v>
       </c>
@@ -8332,7 +8336,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>111</v>
       </c>
@@ -8352,7 +8356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>505</v>
       </c>
@@ -8372,7 +8376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>111</v>
       </c>
@@ -8392,7 +8396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>172</v>
       </c>
@@ -8412,7 +8416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>505</v>
       </c>
@@ -8432,7 +8436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
         <v>222</v>
       </c>
@@ -8452,7 +8456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>222</v>
       </c>
@@ -8472,7 +8476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
         <v>56</v>
       </c>
@@ -8490,7 +8494,7 @@
       </c>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>172</v>
       </c>
@@ -8508,7 +8512,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>56</v>
       </c>
@@ -8528,7 +8532,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
         <v>146</v>
       </c>
@@ -8548,7 +8552,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
         <v>146</v>
       </c>
@@ -8568,7 +8572,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>172</v>
       </c>
@@ -8588,7 +8592,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
         <v>172</v>
       </c>
@@ -8608,7 +8612,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>172</v>
       </c>
@@ -8628,7 +8632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
         <v>222</v>
       </c>
@@ -8646,7 +8650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>505</v>
       </c>
@@ -8666,7 +8670,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
         <v>111</v>
       </c>
@@ -8686,7 +8690,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="299" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
         <v>146</v>
       </c>
@@ -8706,7 +8710,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="300" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -8726,7 +8730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>6</v>
       </c>
@@ -8746,7 +8750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="302" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>172</v>
       </c>
@@ -8766,7 +8770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
         <v>6</v>
       </c>
@@ -8786,7 +8790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>146</v>
       </c>
@@ -8804,7 +8808,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
         <v>6</v>
       </c>
@@ -8822,7 +8826,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
         <v>505</v>
       </c>
@@ -8842,7 +8846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
         <v>56</v>
       </c>
@@ -8862,7 +8866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
         <v>222</v>
       </c>
@@ -8882,7 +8886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>146</v>
       </c>
@@ -8902,7 +8906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
         <v>56</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>505</v>
       </c>
@@ -8942,7 +8946,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
         <v>146</v>
       </c>
@@ -8962,7 +8966,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
         <v>263</v>
       </c>
@@ -8982,7 +8986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>222</v>
       </c>
@@ -9002,7 +9006,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
         <v>712</v>
       </c>
@@ -9022,7 +9026,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
         <v>146</v>
       </c>
@@ -9042,7 +9046,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>263</v>
       </c>
@@ -9062,7 +9066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
         <v>172</v>
       </c>
@@ -9082,7 +9086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>6</v>
       </c>
@@ -9102,7 +9106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>222</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
         <v>263</v>
       </c>
@@ -9142,7 +9146,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
         <v>263</v>
       </c>
@@ -9162,7 +9166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
         <v>111</v>
       </c>
@@ -9182,7 +9186,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>172</v>
       </c>
@@ -9202,7 +9206,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>505</v>
       </c>
@@ -9222,7 +9226,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>222</v>
       </c>
@@ -9242,7 +9246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>263</v>
       </c>
@@ -9262,7 +9266,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>222</v>
       </c>
@@ -9282,7 +9286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
         <v>6</v>
       </c>
@@ -9302,7 +9306,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
         <v>712</v>
       </c>
@@ -9322,7 +9326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
         <v>712</v>
       </c>
@@ -9342,7 +9346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>712</v>
       </c>
@@ -9362,7 +9366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>56</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
         <v>146</v>
       </c>
@@ -9402,7 +9406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
         <v>172</v>
       </c>
@@ -9422,7 +9426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
         <v>172</v>
       </c>
@@ -9442,7 +9446,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
         <v>56</v>
       </c>
@@ -9462,7 +9466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
         <v>111</v>
       </c>
@@ -9482,7 +9486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
         <v>146</v>
       </c>
@@ -9502,7 +9506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
         <v>172</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
         <v>56</v>
       </c>
@@ -9542,7 +9546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>6</v>
       </c>
@@ -9562,7 +9566,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>172</v>
       </c>
@@ -9582,7 +9586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
         <v>505</v>
       </c>
@@ -9602,7 +9606,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>222</v>
       </c>
@@ -9622,7 +9626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>146</v>
       </c>
@@ -9662,7 +9666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
         <v>505</v>
       </c>
@@ -9682,7 +9686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>505</v>
       </c>
@@ -9702,7 +9706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>56</v>
       </c>
@@ -9722,7 +9726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>146</v>
       </c>
@@ -9742,7 +9746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
         <v>56</v>
       </c>
@@ -9760,7 +9764,7 @@
       </c>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
         <v>6</v>
       </c>
@@ -9780,7 +9784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
         <v>222</v>
       </c>
@@ -9800,7 +9804,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
         <v>172</v>
       </c>
@@ -9820,7 +9824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
         <v>172</v>
       </c>
@@ -9840,7 +9844,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>222</v>
       </c>
@@ -9860,7 +9864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
         <v>56</v>
       </c>
@@ -9880,7 +9884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>146</v>
       </c>
@@ -9900,7 +9904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>111</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
         <v>263</v>
       </c>
@@ -9940,7 +9944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>56</v>
       </c>
@@ -9960,7 +9964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>172</v>
       </c>
@@ -9980,7 +9984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>146</v>
       </c>
@@ -10000,7 +10004,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>505</v>
       </c>
@@ -10020,7 +10024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
         <v>222</v>
       </c>
@@ -10040,7 +10044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>6</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
         <v>56</v>
       </c>
@@ -10080,7 +10084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
         <v>146</v>
       </c>
@@ -10100,7 +10104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>146</v>
       </c>
@@ -10118,7 +10122,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
         <v>222</v>
       </c>
@@ -10138,7 +10142,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
         <v>111</v>
       </c>
@@ -10158,7 +10162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
         <v>111</v>
       </c>
@@ -10178,7 +10182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
         <v>222</v>
       </c>
@@ -10198,7 +10202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>146</v>
       </c>
@@ -10218,7 +10222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -10238,7 +10242,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>222</v>
       </c>
@@ -10258,7 +10262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>56</v>
       </c>
@@ -10278,7 +10282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
         <v>505</v>
       </c>
@@ -10298,7 +10302,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
         <v>222</v>
       </c>
@@ -10318,7 +10322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>146</v>
       </c>
@@ -10338,7 +10342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
         <v>505</v>
       </c>
@@ -10358,7 +10362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>56</v>
       </c>
@@ -10378,7 +10382,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>222</v>
       </c>
@@ -10398,7 +10402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="385" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>6</v>
       </c>
@@ -10418,7 +10422,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="386" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>222</v>
       </c>
@@ -10436,7 +10440,7 @@
       </c>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>56</v>
       </c>
@@ -10456,7 +10460,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>263</v>
       </c>
@@ -10476,7 +10480,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="389" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>222</v>
       </c>
@@ -10496,7 +10500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>222</v>
       </c>
@@ -10516,7 +10520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="391" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>6</v>
       </c>
@@ -10536,7 +10540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>56</v>
       </c>
@@ -10576,7 +10580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="394" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>146</v>
       </c>
@@ -10596,7 +10600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>6</v>
       </c>
@@ -10616,7 +10620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="396" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>172</v>
       </c>
@@ -10636,7 +10640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="397" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>172</v>
       </c>
@@ -10656,7 +10660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>222</v>
       </c>
@@ -10676,7 +10680,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="399" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>172</v>
       </c>
@@ -10696,7 +10700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="400" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>222</v>
       </c>
@@ -10716,7 +10720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>146</v>
       </c>
@@ -10736,7 +10740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>111</v>
       </c>
@@ -10756,7 +10760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
         <v>146</v>
       </c>
@@ -10774,7 +10778,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>222</v>
       </c>
@@ -10792,7 +10796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="405" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
         <v>146</v>
       </c>
@@ -10810,7 +10814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="406" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>6</v>
       </c>
@@ -10830,7 +10834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
         <v>505</v>
       </c>
@@ -10850,7 +10854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="408" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
         <v>6</v>
       </c>
@@ -10870,7 +10874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
         <v>146</v>
       </c>
@@ -10890,7 +10894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="410" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
         <v>56</v>
       </c>
@@ -10910,7 +10914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="411" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
         <v>146</v>
       </c>
@@ -10930,7 +10934,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
         <v>222</v>
       </c>
@@ -10950,7 +10954,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>172</v>
       </c>
@@ -10970,7 +10974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>263</v>
       </c>
@@ -10988,7 +10992,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>222</v>
       </c>
@@ -11006,7 +11010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
         <v>6</v>
       </c>
@@ -11024,7 +11028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="417" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
         <v>146</v>
       </c>
@@ -11044,7 +11048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
         <v>712</v>
       </c>
@@ -11062,7 +11066,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="419" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>712</v>
       </c>
@@ -11080,7 +11084,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="420" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>263</v>
       </c>
@@ -11100,7 +11104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
         <v>505</v>
       </c>
@@ -11120,7 +11124,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="422" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
         <v>6</v>
       </c>
@@ -11140,7 +11144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="423" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
         <v>111</v>
       </c>
@@ -11160,7 +11164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="424" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
         <v>263</v>
       </c>
@@ -11180,7 +11184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="425" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
         <v>172</v>
       </c>
@@ -11200,7 +11204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="426" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
         <v>172</v>
       </c>
@@ -11220,7 +11224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="427" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>505</v>
       </c>
@@ -11240,7 +11244,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="428" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
         <v>111</v>
       </c>
@@ -11260,7 +11264,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="429" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>6</v>
       </c>
@@ -11278,7 +11282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="430" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
         <v>6</v>
       </c>
@@ -11298,7 +11302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="431" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
         <v>146</v>
       </c>
@@ -11318,7 +11322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
         <v>263</v>
       </c>
@@ -11338,7 +11342,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="433" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
         <v>172</v>
       </c>
@@ -11358,7 +11362,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="434" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>505</v>
       </c>
@@ -11398,7 +11402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="436" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>263</v>
       </c>
@@ -11418,7 +11422,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
         <v>505</v>
       </c>
@@ -11438,7 +11442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="438" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
         <v>222</v>
       </c>
@@ -11458,7 +11462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="439" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
         <v>146</v>
       </c>
@@ -11478,7 +11482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
         <v>172</v>
       </c>
@@ -11498,7 +11502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
         <v>263</v>
       </c>
@@ -11518,7 +11522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="442" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
         <v>172</v>
       </c>
@@ -11538,7 +11542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="443" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
         <v>111</v>
       </c>
@@ -11558,7 +11562,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="444" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
         <v>146</v>
       </c>
@@ -11578,7 +11582,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="445" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
         <v>505</v>
       </c>
@@ -11598,7 +11602,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="446" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
         <v>146</v>
       </c>
@@ -11618,7 +11622,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="447" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
         <v>111</v>
       </c>
@@ -11638,7 +11642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
         <v>146</v>
       </c>
@@ -11658,7 +11662,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="449" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
         <v>172</v>
       </c>
@@ -11678,7 +11682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="450" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
         <v>6</v>
       </c>
@@ -11698,7 +11702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="451" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
         <v>505</v>
       </c>
@@ -11718,7 +11722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
         <v>111</v>
       </c>
@@ -11738,7 +11742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
         <v>172</v>
       </c>
@@ -11758,7 +11762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="454" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
         <v>222</v>
       </c>
@@ -11778,7 +11782,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="455" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>222</v>
       </c>
@@ -11798,7 +11802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
         <v>111</v>
       </c>
@@ -11816,7 +11820,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
         <v>146</v>
       </c>
@@ -11834,7 +11838,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
         <v>172</v>
       </c>
@@ -11852,7 +11856,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="459" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
         <v>505</v>
       </c>
@@ -11872,7 +11876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="460" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
         <v>146</v>
       </c>
@@ -11892,7 +11896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="461" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
         <v>222</v>
       </c>
@@ -11932,7 +11936,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="463" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
         <v>222</v>
       </c>
@@ -11952,7 +11956,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
         <v>6</v>
       </c>
@@ -11992,7 +11996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="466" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
         <v>222</v>
       </c>
@@ -12012,7 +12016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="467" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
         <v>146</v>
       </c>
@@ -12032,7 +12036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
         <v>505</v>
       </c>
@@ -12052,7 +12056,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
         <v>712</v>
       </c>
@@ -12072,7 +12076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="470" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
         <v>111</v>
       </c>
@@ -12092,7 +12096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="471" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
         <v>56</v>
       </c>
@@ -12112,7 +12116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
         <v>222</v>
       </c>
@@ -12132,7 +12136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
         <v>111</v>
       </c>
@@ -12152,7 +12156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
         <v>263</v>
       </c>
@@ -12172,7 +12176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="475" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>222</v>
       </c>
@@ -12192,7 +12196,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="476" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
         <v>146</v>
       </c>
@@ -12212,7 +12216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="477" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
         <v>6</v>
       </c>
@@ -12232,7 +12236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="478" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
         <v>111</v>
       </c>
@@ -12250,7 +12254,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
         <v>263</v>
       </c>
@@ -12268,7 +12272,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="480" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
         <v>172</v>
       </c>
@@ -12288,7 +12292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="481" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
         <v>6</v>
       </c>
@@ -12306,7 +12310,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="482" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
         <v>263</v>
       </c>
@@ -12326,7 +12330,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="483" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
         <v>6</v>
       </c>
@@ -12344,7 +12348,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="484" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
         <v>505</v>
       </c>
@@ -12364,7 +12368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="485" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
         <v>6</v>
       </c>
@@ -12384,7 +12388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="486" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
         <v>712</v>
       </c>
@@ -12404,7 +12408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
         <v>146</v>
       </c>
@@ -12444,7 +12448,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="489" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
         <v>222</v>
       </c>
@@ -12464,7 +12468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="490" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
         <v>505</v>
       </c>
@@ -12484,7 +12488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="491" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
         <v>56</v>
       </c>
@@ -12504,7 +12508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="492" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
         <v>111</v>
       </c>
@@ -12524,7 +12528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="493" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
         <v>222</v>
       </c>
@@ -12544,7 +12548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="494" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
         <v>56</v>
       </c>
@@ -12564,7 +12568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="495" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
         <v>172</v>
       </c>
@@ -12584,7 +12588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="496" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
         <v>6</v>
       </c>
@@ -12604,7 +12608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
         <v>222</v>
       </c>
@@ -12624,7 +12628,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="498" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
         <v>6</v>
       </c>
@@ -12642,7 +12646,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="499" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
         <v>146</v>
       </c>
@@ -12662,7 +12666,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="500" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
         <v>111</v>
       </c>
@@ -12682,7 +12686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="501" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
         <v>263</v>
       </c>
@@ -12702,7 +12706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="502" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
         <v>712</v>
       </c>
@@ -12722,7 +12726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="503" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
         <v>146</v>
       </c>
@@ -12742,7 +12746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="504" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
         <v>222</v>
       </c>
@@ -12762,7 +12766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
         <v>146</v>
       </c>
@@ -12782,7 +12786,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="506" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
         <v>222</v>
       </c>
@@ -12800,7 +12804,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="507" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
         <v>111</v>
       </c>
@@ -12820,7 +12824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="508" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
         <v>505</v>
       </c>
@@ -12840,7 +12844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="509" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
         <v>111</v>
       </c>
@@ -12860,7 +12864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="510" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
         <v>146</v>
       </c>
@@ -12880,7 +12884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="511" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
         <v>56</v>
       </c>
@@ -12900,7 +12904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="512" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
         <v>263</v>
       </c>
@@ -12920,7 +12924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="513" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
         <v>111</v>
       </c>
@@ -12940,7 +12944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
         <v>6</v>
       </c>
@@ -12960,7 +12964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="515" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
         <v>6</v>
       </c>
@@ -12978,7 +12982,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="516" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
         <v>263</v>
       </c>
@@ -12998,7 +13002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="517" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
         <v>146</v>
       </c>
@@ -13018,7 +13022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="518" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
         <v>6</v>
       </c>
@@ -13038,7 +13042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="519" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
         <v>505</v>
       </c>
@@ -13058,7 +13062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
         <v>505</v>
       </c>
@@ -13078,7 +13082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="521" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
         <v>56</v>
       </c>
@@ -13118,7 +13122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="523" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
         <v>146</v>
       </c>
@@ -13138,7 +13142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="524" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
         <v>263</v>
       </c>
@@ -13158,7 +13162,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="525" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
         <v>111</v>
       </c>
@@ -13178,7 +13182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="526" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
         <v>56</v>
       </c>
@@ -13198,7 +13202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="527" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
         <v>146</v>
       </c>
@@ -13238,7 +13242,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="529" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
         <v>111</v>
       </c>
@@ -13258,7 +13262,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
         <v>56</v>
       </c>
@@ -13278,7 +13282,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>222</v>
       </c>
@@ -13298,7 +13302,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="532" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
         <v>146</v>
       </c>
@@ -13318,7 +13322,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="533" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
         <v>172</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="534" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
         <v>111</v>
       </c>
@@ -13358,7 +13362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="535" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>146</v>
       </c>
@@ -13378,7 +13382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="536" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
         <v>56</v>
       </c>
@@ -13398,7 +13402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="537" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
         <v>505</v>
       </c>
@@ -13418,7 +13422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="538" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
         <v>111</v>
       </c>
@@ -13438,7 +13442,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="539" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
         <v>56</v>
       </c>
@@ -13456,7 +13460,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="540" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="s">
         <v>56</v>
       </c>
@@ -13476,7 +13480,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="541" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="s">
         <v>222</v>
       </c>
@@ -13496,7 +13500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="542" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="s">
         <v>712</v>
       </c>
@@ -13516,7 +13520,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="s">
         <v>712</v>
       </c>
@@ -13536,7 +13540,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="544" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="s">
         <v>172</v>
       </c>
@@ -13556,7 +13560,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="545" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="s">
         <v>111</v>
       </c>
@@ -13596,7 +13600,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="547" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="s">
         <v>712</v>
       </c>
@@ -13616,7 +13620,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="s">
         <v>56</v>
       </c>
@@ -13636,7 +13640,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="549" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>146</v>
       </c>
@@ -13656,7 +13660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="550" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
         <v>505</v>
       </c>
@@ -13696,7 +13700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="552" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="s">
         <v>222</v>
       </c>
@@ -13716,7 +13720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="s">
         <v>172</v>
       </c>
@@ -13736,7 +13740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="1" t="s">
         <v>56</v>
       </c>
@@ -13756,7 +13760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="555" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="1" t="s">
         <v>505</v>
       </c>
@@ -13794,7 +13798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="1" t="s">
         <v>505</v>
       </c>
@@ -13814,7 +13818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="1" t="s">
         <v>263</v>
       </c>
@@ -13834,7 +13838,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="559" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="1" t="s">
         <v>172</v>
       </c>
@@ -13854,7 +13858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="560" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="1" t="s">
         <v>146</v>
       </c>
@@ -13874,7 +13878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="1" t="s">
         <v>146</v>
       </c>
@@ -13894,7 +13898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="1" t="s">
         <v>172</v>
       </c>
@@ -13914,7 +13918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="563" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="s">
         <v>56</v>
       </c>
@@ -13934,7 +13938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="564" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="s">
         <v>222</v>
       </c>
@@ -13954,7 +13958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="1" t="s">
         <v>172</v>
       </c>
@@ -13994,7 +13998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="1" t="s">
         <v>222</v>
       </c>
@@ -14014,7 +14018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="568" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="1" t="s">
         <v>172</v>
       </c>
@@ -14034,7 +14038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="569" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="1" t="s">
         <v>146</v>
       </c>
@@ -14054,7 +14058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="570" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="1" t="s">
         <v>505</v>
       </c>
@@ -14074,7 +14078,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="571" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="1" t="s">
         <v>6</v>
       </c>
@@ -14094,7 +14098,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="572" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="1" t="s">
         <v>146</v>
       </c>
@@ -14114,7 +14118,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="573" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="1" t="s">
         <v>56</v>
       </c>
@@ -14134,7 +14138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="574" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="1" t="s">
         <v>222</v>
       </c>
@@ -14154,7 +14158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="575" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="s">
         <v>111</v>
       </c>
@@ -14194,7 +14198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="577" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="1" t="s">
         <v>222</v>
       </c>
@@ -14214,7 +14218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="578" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="1" t="s">
         <v>712</v>
       </c>
@@ -14234,7 +14238,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="579" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="1" t="s">
         <v>222</v>
       </c>
@@ -14254,7 +14258,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="580" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="1" t="s">
         <v>111</v>
       </c>
@@ -14274,7 +14278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="581" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="1" t="s">
         <v>56</v>
       </c>
@@ -14294,7 +14298,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="582" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="1" t="s">
         <v>146</v>
       </c>
@@ -14314,7 +14318,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="583" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="1" t="s">
         <v>222</v>
       </c>
@@ -14334,7 +14338,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="584" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="1" t="s">
         <v>56</v>
       </c>
@@ -14354,7 +14358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="585" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="1" t="s">
         <v>146</v>
       </c>
@@ -14374,7 +14378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="586" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="1" t="s">
         <v>6</v>
       </c>
@@ -14394,7 +14398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="587" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="1" t="s">
         <v>172</v>
       </c>
@@ -14414,7 +14418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="588" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="1" t="s">
         <v>6</v>
       </c>
@@ -14432,7 +14436,7 @@
       </c>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="1" t="s">
         <v>146</v>
       </c>
@@ -14450,7 +14454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="590" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="1" t="s">
         <v>263</v>
       </c>
@@ -14470,7 +14474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="591" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="1" t="s">
         <v>56</v>
       </c>
@@ -14490,7 +14494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="592" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="1" t="s">
         <v>172</v>
       </c>
@@ -14510,7 +14514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="593" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="1" t="s">
         <v>263</v>
       </c>
@@ -14530,7 +14534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="594" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="1" t="s">
         <v>146</v>
       </c>
@@ -14550,7 +14554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="595" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="1" t="s">
         <v>172</v>
       </c>
@@ -14570,7 +14574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="596" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="1" t="s">
         <v>146</v>
       </c>
@@ -14590,7 +14594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="597" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="1" t="s">
         <v>505</v>
       </c>
@@ -14610,7 +14614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="598" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="1" t="s">
         <v>111</v>
       </c>
@@ -14630,7 +14634,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="599" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="1" t="s">
         <v>263</v>
       </c>
@@ -14650,7 +14654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="600" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="1" t="s">
         <v>56</v>
       </c>
@@ -14688,7 +14692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="602" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="1" t="s">
         <v>222</v>
       </c>
@@ -14708,7 +14712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="603" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="1" t="s">
         <v>56</v>
       </c>
@@ -14728,7 +14732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="604" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="1" t="s">
         <v>222</v>
       </c>
@@ -14748,7 +14752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="605" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="1" t="s">
         <v>146</v>
       </c>
@@ -14768,7 +14772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="606" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="1" t="s">
         <v>172</v>
       </c>
@@ -14788,7 +14792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="607" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" s="1" t="s">
         <v>505</v>
       </c>
@@ -14808,7 +14812,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="608" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" s="1" t="s">
         <v>56</v>
       </c>
@@ -14828,7 +14832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="609" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="1" t="s">
         <v>6</v>
       </c>
@@ -14848,7 +14852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="610" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="1" t="s">
         <v>56</v>
       </c>
@@ -14868,7 +14872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="611" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" s="1" t="s">
         <v>505</v>
       </c>
@@ -14888,7 +14892,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="612" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" s="1" t="s">
         <v>222</v>
       </c>
@@ -14908,7 +14912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="613" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" s="1" t="s">
         <v>505</v>
       </c>
@@ -14928,7 +14932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="614" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" s="1" t="s">
         <v>111</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="615" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" s="1" t="s">
         <v>222</v>
       </c>
@@ -14968,7 +14972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="616" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="1" t="s">
         <v>6</v>
       </c>
@@ -14988,7 +14992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="617" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="1" t="s">
         <v>56</v>
       </c>
@@ -15008,7 +15012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="618" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" s="1" t="s">
         <v>146</v>
       </c>
@@ -15028,7 +15032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="619" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="1" t="s">
         <v>505</v>
       </c>
@@ -15048,7 +15052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" s="1" t="s">
         <v>146</v>
       </c>
@@ -15068,7 +15072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="621" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" s="1" t="s">
         <v>222</v>
       </c>
@@ -15086,7 +15090,7 @@
       </c>
       <c r="F621" s="3"/>
     </row>
-    <row r="622" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" s="1" t="s">
         <v>712</v>
       </c>
@@ -15106,7 +15110,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="623" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" s="1" t="s">
         <v>111</v>
       </c>
@@ -15126,7 +15130,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="624" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" s="1" t="s">
         <v>222</v>
       </c>
@@ -15146,7 +15150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="625" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" s="1" t="s">
         <v>172</v>
       </c>
@@ -15166,7 +15170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="626" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="1" t="s">
         <v>505</v>
       </c>
@@ -15186,7 +15190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="627" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="1" t="s">
         <v>146</v>
       </c>
@@ -15206,7 +15210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="628" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="1" t="s">
         <v>222</v>
       </c>
@@ -15226,7 +15230,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="629" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="1" t="s">
         <v>6</v>
       </c>
@@ -15244,7 +15248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="630" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="1" t="s">
         <v>172</v>
       </c>
@@ -15262,7 +15266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="631" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" s="1" t="s">
         <v>505</v>
       </c>
@@ -15280,7 +15284,7 @@
       </c>
       <c r="F631" s="3"/>
     </row>
-    <row r="632" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="1" t="s">
         <v>505</v>
       </c>
@@ -15298,7 +15302,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="633" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="1" t="s">
         <v>146</v>
       </c>
@@ -15318,7 +15322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="634" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="1" t="s">
         <v>56</v>
       </c>
@@ -15338,7 +15342,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="635" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="1" t="s">
         <v>222</v>
       </c>
@@ -15358,7 +15362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="636" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="1" t="s">
         <v>505</v>
       </c>
@@ -15378,7 +15382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="637" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="1" t="s">
         <v>172</v>
       </c>
@@ -15398,7 +15402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="638" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="1" t="s">
         <v>111</v>
       </c>
@@ -15418,7 +15422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="639" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="1" t="s">
         <v>222</v>
       </c>
@@ -15438,7 +15442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="640" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" s="1" t="s">
         <v>146</v>
       </c>
@@ -15478,7 +15482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="642" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" s="1" t="s">
         <v>146</v>
       </c>
@@ -15498,7 +15502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="643" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="1" t="s">
         <v>6</v>
       </c>
@@ -15518,7 +15522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="644" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" s="1" t="s">
         <v>712</v>
       </c>
@@ -15538,7 +15542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="645" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" s="1" t="s">
         <v>712</v>
       </c>
@@ -15558,7 +15562,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="646" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" s="1" t="s">
         <v>146</v>
       </c>
@@ -15596,7 +15600,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" s="1" t="s">
         <v>222</v>
       </c>
@@ -15616,7 +15620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="649" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="1" t="s">
         <v>6</v>
       </c>
@@ -15634,7 +15638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="650" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="1" t="s">
         <v>263</v>
       </c>
@@ -15654,7 +15658,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="651" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="1" t="s">
         <v>172</v>
       </c>
@@ -15674,7 +15678,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="652" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="1" t="s">
         <v>56</v>
       </c>
@@ -15694,7 +15698,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="653" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="1" t="s">
         <v>222</v>
       </c>
@@ -15714,7 +15718,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="1" t="s">
         <v>6</v>
       </c>
@@ -15734,7 +15738,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="655" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="1" t="s">
         <v>505</v>
       </c>
@@ -15754,7 +15758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="656" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" s="1" t="s">
         <v>263</v>
       </c>
@@ -15774,7 +15778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="657" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="1" t="s">
         <v>505</v>
       </c>
@@ -15794,7 +15798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="658" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="s">
         <v>146</v>
       </c>
@@ -15814,7 +15818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="659" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="1" t="s">
         <v>146</v>
       </c>
@@ -15834,7 +15838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="660" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="1" t="s">
         <v>263</v>
       </c>
@@ -15854,7 +15858,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="661" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" s="1" t="s">
         <v>56</v>
       </c>
@@ -15874,7 +15878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="662" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" s="1" t="s">
         <v>6</v>
       </c>
@@ -15894,7 +15898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="663" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="1" t="s">
         <v>172</v>
       </c>
@@ -15914,7 +15918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="664" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="1" t="s">
         <v>505</v>
       </c>
@@ -15932,7 +15936,7 @@
       </c>
       <c r="F664" s="3"/>
     </row>
-    <row r="665" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="1" t="s">
         <v>222</v>
       </c>
@@ -15952,7 +15956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="666" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="1" t="s">
         <v>146</v>
       </c>
@@ -15972,7 +15976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="667" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="1" t="s">
         <v>6</v>
       </c>
@@ -15992,7 +15996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="668" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" s="1" t="s">
         <v>6</v>
       </c>
@@ -16010,7 +16014,7 @@
       </c>
       <c r="F668" s="3"/>
     </row>
-    <row r="669" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" s="1" t="s">
         <v>56</v>
       </c>
@@ -16030,7 +16034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="670" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="1" t="s">
         <v>6</v>
       </c>
@@ -16050,7 +16054,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="671" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" s="1" t="s">
         <v>505</v>
       </c>
@@ -16070,7 +16074,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="672" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="1" t="s">
         <v>222</v>
       </c>
@@ -16090,7 +16094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="673" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="1" t="s">
         <v>146</v>
       </c>
@@ -16110,7 +16114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="674" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" s="1" t="s">
         <v>172</v>
       </c>
@@ -16130,7 +16134,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="675" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" s="1" t="s">
         <v>146</v>
       </c>
@@ -16150,7 +16154,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="676" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="1" t="s">
         <v>172</v>
       </c>
@@ -16170,7 +16174,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="677" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" s="1" t="s">
         <v>172</v>
       </c>
@@ -16190,7 +16194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="678" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="1" t="s">
         <v>172</v>
       </c>
@@ -16210,7 +16214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="679" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" s="1" t="s">
         <v>6</v>
       </c>
@@ -16230,7 +16234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="680" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" s="1" t="s">
         <v>6</v>
       </c>
@@ -16250,7 +16254,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="681" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" s="1" t="s">
         <v>146</v>
       </c>
@@ -16270,7 +16274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="682" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" s="1" t="s">
         <v>146</v>
       </c>
@@ -16290,7 +16294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="683" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" s="1" t="s">
         <v>222</v>
       </c>
@@ -16310,7 +16314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="684" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="1" t="s">
         <v>111</v>
       </c>
@@ -16330,7 +16334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="685" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="1" t="s">
         <v>146</v>
       </c>
@@ -16350,7 +16354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="686" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" s="1" t="s">
         <v>222</v>
       </c>
@@ -16368,7 +16372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="687" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" s="1" t="s">
         <v>222</v>
       </c>
@@ -16386,7 +16390,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="688" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" s="1" t="s">
         <v>6</v>
       </c>
@@ -16404,7 +16408,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="689" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" s="1" t="s">
         <v>56</v>
       </c>
@@ -16424,7 +16428,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="690" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="1" t="s">
         <v>712</v>
       </c>
@@ -16442,7 +16446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="691" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="1" t="s">
         <v>712</v>
       </c>
@@ -16460,7 +16464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="692" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" s="1" t="s">
         <v>263</v>
       </c>
@@ -16480,7 +16484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="693" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" s="1" t="s">
         <v>56</v>
       </c>
@@ -16500,7 +16504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="694" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" s="1" t="s">
         <v>222</v>
       </c>
@@ -16520,7 +16524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="695" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" s="1" t="s">
         <v>222</v>
       </c>
@@ -16540,7 +16544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="696" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" s="1" t="s">
         <v>146</v>
       </c>
@@ -16558,7 +16562,7 @@
       </c>
       <c r="F696" s="3"/>
     </row>
-    <row r="697" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="1" t="s">
         <v>6</v>
       </c>
@@ -16578,7 +16582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="698" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="1" t="s">
         <v>263</v>
       </c>
@@ -16598,7 +16602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="699" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" s="1" t="s">
         <v>56</v>
       </c>
@@ -16618,7 +16622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="700" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="1" t="s">
         <v>111</v>
       </c>
@@ -16638,7 +16642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="701" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="1" t="s">
         <v>712</v>
       </c>
@@ -16658,7 +16662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="702" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="1" t="s">
         <v>146</v>
       </c>
@@ -16678,7 +16682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="703" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" s="1" t="s">
         <v>146</v>
       </c>
@@ -16698,7 +16702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="704" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="1" t="s">
         <v>172</v>
       </c>
@@ -16718,7 +16722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="705" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="1" t="s">
         <v>6</v>
       </c>
@@ -16738,7 +16742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="706" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="1" t="s">
         <v>172</v>
       </c>
@@ -16798,7 +16802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="709" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="1" t="s">
         <v>111</v>
       </c>
@@ -16818,7 +16822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="710" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="1" t="s">
         <v>111</v>
       </c>
@@ -16838,7 +16842,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="711" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="1" t="s">
         <v>712</v>
       </c>
@@ -16858,7 +16862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="712" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="1" t="s">
         <v>6</v>
       </c>
@@ -16876,7 +16880,7 @@
       </c>
       <c r="F712" s="3"/>
     </row>
-    <row r="713" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="1" t="s">
         <v>712</v>
       </c>
@@ -16896,7 +16900,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="714" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="1" t="s">
         <v>712</v>
       </c>
@@ -16916,7 +16920,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="715" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="1" t="s">
         <v>56</v>
       </c>
@@ -16952,7 +16956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="717" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" s="1" t="s">
         <v>222</v>
       </c>
@@ -16970,7 +16974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="718" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" s="1" t="s">
         <v>146</v>
       </c>
@@ -16988,7 +16992,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="719" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" s="1" t="s">
         <v>172</v>
       </c>
@@ -17006,7 +17010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="720" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" s="1" t="s">
         <v>505</v>
       </c>
@@ -17026,7 +17030,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="721" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" s="1" t="s">
         <v>222</v>
       </c>
@@ -17046,7 +17050,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="722" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" s="1" t="s">
         <v>222</v>
       </c>
@@ -17064,7 +17068,7 @@
       </c>
       <c r="F722" s="3"/>
     </row>
-    <row r="723" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" s="1" t="s">
         <v>263</v>
       </c>
@@ -17084,7 +17088,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="724" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" s="1" t="s">
         <v>56</v>
       </c>
@@ -17104,7 +17108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="725" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" s="1" t="s">
         <v>222</v>
       </c>
@@ -17124,7 +17128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="726" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" s="1" t="s">
         <v>172</v>
       </c>
@@ -17144,7 +17148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="727" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" s="1" t="s">
         <v>172</v>
       </c>
@@ -17164,7 +17168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="728" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" s="1" t="s">
         <v>146</v>
       </c>
@@ -17184,7 +17188,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="729" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" s="1" t="s">
         <v>6</v>
       </c>
@@ -17204,7 +17208,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="730" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" s="1" t="s">
         <v>222</v>
       </c>
@@ -17224,7 +17228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="731" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" s="1" t="s">
         <v>6</v>
       </c>
@@ -17244,7 +17248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="732" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" s="1" t="s">
         <v>111</v>
       </c>
@@ -17264,7 +17268,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="733" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" s="1" t="s">
         <v>263</v>
       </c>
@@ -17284,7 +17288,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="734" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" s="1" t="s">
         <v>505</v>
       </c>
@@ -17304,7 +17308,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="735" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" s="1" t="s">
         <v>6</v>
       </c>
@@ -17324,7 +17328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="736" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" s="1" t="s">
         <v>172</v>
       </c>
@@ -17344,7 +17348,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="737" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" s="1" t="s">
         <v>6</v>
       </c>
@@ -17364,7 +17368,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="738" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" s="1" t="s">
         <v>222</v>
       </c>
@@ -17384,7 +17388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="739" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" s="1" t="s">
         <v>56</v>
       </c>
@@ -17404,7 +17408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="740" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" s="1" t="s">
         <v>222</v>
       </c>
@@ -17424,7 +17428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="741" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" s="1" t="s">
         <v>146</v>
       </c>
@@ -17444,7 +17448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="742" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" s="1" t="s">
         <v>56</v>
       </c>
@@ -17464,7 +17468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="743" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" s="1" t="s">
         <v>146</v>
       </c>
@@ -17484,7 +17488,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="744" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" s="1" t="s">
         <v>146</v>
       </c>
@@ -17504,7 +17508,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="745" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" s="1" t="s">
         <v>222</v>
       </c>
@@ -17524,7 +17528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="746" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" s="1" t="s">
         <v>146</v>
       </c>
@@ -17564,7 +17568,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="748" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" s="1" t="s">
         <v>505</v>
       </c>
@@ -17584,7 +17588,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="749" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" s="1" t="s">
         <v>56</v>
       </c>
@@ -17604,7 +17608,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="750" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" s="1" t="s">
         <v>263</v>
       </c>
@@ -17624,7 +17628,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="751" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" s="1" t="s">
         <v>172</v>
       </c>
@@ -17644,7 +17648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="752" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" s="1" t="s">
         <v>111</v>
       </c>
@@ -17664,7 +17668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="753" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" s="1" t="s">
         <v>222</v>
       </c>
@@ -17684,7 +17688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="754" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" s="1" t="s">
         <v>146</v>
       </c>
@@ -17704,7 +17708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="755" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" s="1" t="s">
         <v>146</v>
       </c>
@@ -17744,7 +17748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="757" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" s="1" t="s">
         <v>172</v>
       </c>
@@ -17764,7 +17768,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="758" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" s="1" t="s">
         <v>505</v>
       </c>
@@ -17784,7 +17788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="759" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" s="1" t="s">
         <v>146</v>
       </c>
@@ -17804,7 +17808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="760" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" s="1" t="s">
         <v>505</v>
       </c>
@@ -17824,7 +17828,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="761" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" s="1" t="s">
         <v>111</v>
       </c>
@@ -17844,7 +17848,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="762" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" s="1" t="s">
         <v>172</v>
       </c>
@@ -17864,7 +17868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="763" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" s="1" t="s">
         <v>505</v>
       </c>
@@ -17884,7 +17888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="764" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" s="1" t="s">
         <v>6</v>
       </c>
@@ -17904,7 +17908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="765" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" s="1" t="s">
         <v>222</v>
       </c>
@@ -17924,7 +17928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="766" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="1" t="s">
         <v>222</v>
       </c>
@@ -17944,7 +17948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="767" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" s="1" t="s">
         <v>146</v>
       </c>
@@ -17964,7 +17968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="768" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" s="1" t="s">
         <v>222</v>
       </c>
@@ -17984,7 +17988,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="769" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" s="1" t="s">
         <v>222</v>
       </c>
@@ -18004,7 +18008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="770" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" s="1" t="s">
         <v>111</v>
       </c>
@@ -18024,7 +18028,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="771" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" s="1" t="s">
         <v>172</v>
       </c>
@@ -18044,7 +18048,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="772" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" s="1" t="s">
         <v>56</v>
       </c>
@@ -18064,7 +18068,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="773" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" s="1" t="s">
         <v>222</v>
       </c>
@@ -18084,7 +18088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="774" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" s="1" t="s">
         <v>111</v>
       </c>
@@ -18104,7 +18108,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="775" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" s="1" t="s">
         <v>146</v>
       </c>
@@ -18124,7 +18128,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="776" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" s="1" t="s">
         <v>56</v>
       </c>
@@ -18144,7 +18148,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="777" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" s="1" t="s">
         <v>111</v>
       </c>
@@ -18164,7 +18168,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="778" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" s="1" t="s">
         <v>111</v>
       </c>
@@ -18200,7 +18204,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="780" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" s="1" t="s">
         <v>56</v>
       </c>
@@ -18220,7 +18224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="781" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" s="1" t="s">
         <v>222</v>
       </c>
@@ -18240,7 +18244,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="782" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" s="1" t="s">
         <v>6</v>
       </c>
@@ -18260,7 +18264,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="783" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" s="1" t="s">
         <v>146</v>
       </c>
@@ -18276,7 +18280,7 @@
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
     </row>
-    <row r="784" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" s="1" t="s">
         <v>6</v>
       </c>
@@ -18296,7 +18300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="785" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" s="1" t="s">
         <v>222</v>
       </c>
@@ -18316,7 +18320,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="786" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" s="1" t="s">
         <v>222</v>
       </c>
@@ -18336,7 +18340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="787" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" s="1" t="s">
         <v>56</v>
       </c>
@@ -18356,7 +18360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="788" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" s="1" t="s">
         <v>222</v>
       </c>
@@ -18376,7 +18380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="789" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" s="1" t="s">
         <v>146</v>
       </c>
@@ -18396,7 +18400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="790" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" s="1" t="s">
         <v>146</v>
       </c>
@@ -18416,7 +18420,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="791" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" s="1" t="s">
         <v>56</v>
       </c>
@@ -18436,7 +18440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="792" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" s="1" t="s">
         <v>56</v>
       </c>
@@ -18454,7 +18458,7 @@
       </c>
       <c r="F792" s="3"/>
     </row>
-    <row r="793" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" s="1" t="s">
         <v>222</v>
       </c>
@@ -18472,7 +18476,7 @@
       </c>
       <c r="F793" s="3"/>
     </row>
-    <row r="794" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="1" t="s">
         <v>222</v>
       </c>
@@ -18512,7 +18516,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="796" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="1" t="s">
         <v>146</v>
       </c>
@@ -18532,7 +18536,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="797" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="1" t="s">
         <v>505</v>
       </c>
@@ -18552,7 +18556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="798" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" s="1" t="s">
         <v>146</v>
       </c>
@@ -18572,7 +18576,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="799" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" s="1" t="s">
         <v>6</v>
       </c>
@@ -18592,7 +18596,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="800" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" s="1" t="s">
         <v>111</v>
       </c>
@@ -18612,7 +18616,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="801" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" s="1" t="s">
         <v>56</v>
       </c>
@@ -18632,7 +18636,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="802" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" s="1" t="s">
         <v>222</v>
       </c>
@@ -18652,7 +18656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="803" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" s="1" t="s">
         <v>146</v>
       </c>
@@ -18672,7 +18676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="804" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" s="1" t="s">
         <v>505</v>
       </c>
@@ -18692,7 +18696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="805" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" s="1" t="s">
         <v>56</v>
       </c>
@@ -18712,7 +18716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="806" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" s="1" t="s">
         <v>222</v>
       </c>
@@ -18732,7 +18736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="807" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" s="1" t="s">
         <v>146</v>
       </c>
@@ -18752,7 +18756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="808" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" s="1" t="s">
         <v>222</v>
       </c>
@@ -18770,7 +18774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="809" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" s="1" t="s">
         <v>56</v>
       </c>
@@ -18790,7 +18794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="810" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" s="1" t="s">
         <v>505</v>
       </c>
@@ -18810,7 +18814,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="811" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" s="1" t="s">
         <v>146</v>
       </c>
@@ -18828,7 +18832,7 @@
       </c>
       <c r="F811" s="3"/>
     </row>
-    <row r="812" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" s="1" t="s">
         <v>146</v>
       </c>
@@ -18848,7 +18852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="813" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A813" s="1" t="s">
         <v>6</v>
       </c>
@@ -18868,7 +18872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="814" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" s="1" t="s">
         <v>172</v>
       </c>
@@ -18888,7 +18892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="815" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" s="1" t="s">
         <v>172</v>
       </c>
@@ -18908,7 +18912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="816" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" s="1" t="s">
         <v>172</v>
       </c>
@@ -18928,7 +18932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="817" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" s="1" t="s">
         <v>222</v>
       </c>
@@ -18948,7 +18952,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="818" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" s="1" t="s">
         <v>56</v>
       </c>
@@ -18968,7 +18972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="819" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A819" s="1" t="s">
         <v>263</v>
       </c>
@@ -18988,7 +18992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="820" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" s="1" t="s">
         <v>263</v>
       </c>
@@ -19008,7 +19012,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="821" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" s="1" t="s">
         <v>56</v>
       </c>
@@ -19028,7 +19032,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="822" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" s="1" t="s">
         <v>505</v>
       </c>
@@ -19046,7 +19050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="823" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A823" s="1" t="s">
         <v>111</v>
       </c>
@@ -19064,7 +19068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="824" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A824" s="1" t="s">
         <v>505</v>
       </c>
@@ -19084,7 +19088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="825" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" s="1" t="s">
         <v>6</v>
       </c>
@@ -19104,7 +19108,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="826" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" s="1" t="s">
         <v>172</v>
       </c>
@@ -19124,7 +19128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="827" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" s="1" t="s">
         <v>111</v>
       </c>
@@ -19144,7 +19148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="828" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" s="1" t="s">
         <v>146</v>
       </c>
@@ -19164,7 +19168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="829" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A829" s="1" t="s">
         <v>6</v>
       </c>
@@ -19184,7 +19188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="830" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" s="1" t="s">
         <v>222</v>
       </c>
@@ -19204,7 +19208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="831" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" s="1" t="s">
         <v>111</v>
       </c>
@@ -19224,7 +19228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="832" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" s="1" t="s">
         <v>6</v>
       </c>
@@ -19244,7 +19248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="833" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" s="1" t="s">
         <v>172</v>
       </c>
@@ -19264,7 +19268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="834" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" s="1" t="s">
         <v>263</v>
       </c>
@@ -19284,7 +19288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="835" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" s="1" t="s">
         <v>146</v>
       </c>
@@ -19304,7 +19308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="836" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" s="1" t="s">
         <v>56</v>
       </c>
@@ -19322,7 +19326,7 @@
       </c>
       <c r="F836" s="3"/>
     </row>
-    <row r="837" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" s="1" t="s">
         <v>56</v>
       </c>
@@ -19342,7 +19346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="838" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A838" s="1" t="s">
         <v>56</v>
       </c>
@@ -19360,7 +19364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="839" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" s="1" t="s">
         <v>6</v>
       </c>
@@ -19378,7 +19382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="840" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" s="1" t="s">
         <v>222</v>
       </c>
@@ -19398,7 +19402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="841" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" s="1" t="s">
         <v>172</v>
       </c>
@@ -19418,7 +19422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="842" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A842" s="1" t="s">
         <v>56</v>
       </c>
@@ -19438,7 +19442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="843" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A843" s="1" t="s">
         <v>111</v>
       </c>
@@ -19458,7 +19462,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="844" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" s="1" t="s">
         <v>146</v>
       </c>
@@ -19478,7 +19482,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="845" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" s="1" t="s">
         <v>222</v>
       </c>
@@ -19498,7 +19502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="846" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" s="1" t="s">
         <v>222</v>
       </c>
@@ -19518,7 +19522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="847" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A847" s="1" t="s">
         <v>146</v>
       </c>
@@ -19538,7 +19542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="848" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" s="1" t="s">
         <v>222</v>
       </c>
@@ -19556,7 +19560,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="849" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A849" s="1" t="s">
         <v>146</v>
       </c>
@@ -19574,7 +19578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="850" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A850" s="1" t="s">
         <v>146</v>
       </c>
@@ -19594,7 +19598,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="851" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" s="1" t="s">
         <v>56</v>
       </c>
@@ -19614,7 +19618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="852" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A852" s="1" t="s">
         <v>505</v>
       </c>
@@ -19634,7 +19638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="853" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" s="1" t="s">
         <v>111</v>
       </c>
@@ -19652,7 +19656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="854" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A854" s="1" t="s">
         <v>505</v>
       </c>
@@ -19692,7 +19696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="856" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" s="1" t="s">
         <v>146</v>
       </c>
@@ -19712,7 +19716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="857" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A857" s="1" t="s">
         <v>172</v>
       </c>
@@ -19732,7 +19736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="858" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" s="1" t="s">
         <v>111</v>
       </c>
@@ -19750,7 +19754,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="859" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A859" s="1" t="s">
         <v>505</v>
       </c>
@@ -19770,7 +19774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="860" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A860" s="1" t="s">
         <v>56</v>
       </c>
@@ -19790,7 +19794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="861" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" s="1" t="s">
         <v>172</v>
       </c>
@@ -19830,7 +19834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="863" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A863" s="1" t="s">
         <v>56</v>
       </c>
@@ -19850,7 +19854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="864" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" s="1" t="s">
         <v>6</v>
       </c>
@@ -19870,7 +19874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="865" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A865" s="1" t="s">
         <v>6</v>
       </c>
@@ -19890,7 +19894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="866" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A866" s="1" t="s">
         <v>505</v>
       </c>
@@ -19910,7 +19914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="867" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A867" s="1" t="s">
         <v>146</v>
       </c>
@@ -19930,7 +19934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="868" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A868" s="1" t="s">
         <v>6</v>
       </c>
@@ -19950,7 +19954,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="869" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A869" s="1" t="s">
         <v>222</v>
       </c>
@@ -19970,7 +19974,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="870" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A870" s="1" t="s">
         <v>505</v>
       </c>
@@ -19990,7 +19994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="871" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A871" s="1" t="s">
         <v>111</v>
       </c>
@@ -20030,7 +20034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="873" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A873" s="1" t="s">
         <v>712</v>
       </c>
@@ -20050,7 +20054,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="874" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A874" s="1" t="s">
         <v>712</v>
       </c>
@@ -20070,7 +20074,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="875" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A875" s="1" t="s">
         <v>712</v>
       </c>
@@ -20090,7 +20094,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="876" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A876" s="1" t="s">
         <v>222</v>
       </c>
@@ -20110,7 +20114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="877" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A877" s="1" t="s">
         <v>56</v>
       </c>
@@ -20130,7 +20134,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="878" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A878" s="1" t="s">
         <v>6</v>
       </c>
@@ -20150,7 +20154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="879" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A879" s="1" t="s">
         <v>56</v>
       </c>
@@ -20170,7 +20174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="880" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A880" s="1" t="s">
         <v>146</v>
       </c>
@@ -20190,7 +20194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="881" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A881" s="1" t="s">
         <v>111</v>
       </c>
@@ -20210,7 +20214,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="882" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A882" s="1" t="s">
         <v>263</v>
       </c>
@@ -20230,7 +20234,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="883" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A883" s="1" t="s">
         <v>146</v>
       </c>
@@ -20250,7 +20254,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="884" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A884" s="1" t="s">
         <v>111</v>
       </c>
@@ -20270,7 +20274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="885" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A885" s="1" t="s">
         <v>222</v>
       </c>
@@ -20290,7 +20294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="886" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A886" s="1" t="s">
         <v>172</v>
       </c>
@@ -20310,7 +20314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="887" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A887" s="1" t="s">
         <v>111</v>
       </c>
@@ -20328,7 +20332,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="888" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A888" s="1" t="s">
         <v>6</v>
       </c>
@@ -20346,7 +20350,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="889" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A889" s="1" t="s">
         <v>505</v>
       </c>
@@ -20366,7 +20370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="890" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A890" s="1" t="s">
         <v>263</v>
       </c>
@@ -20386,7 +20390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="891" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A891" s="1" t="s">
         <v>56</v>
       </c>
@@ -20406,7 +20410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="892" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A892" s="1" t="s">
         <v>146</v>
       </c>
@@ -20426,7 +20430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="893" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A893" s="1" t="s">
         <v>56</v>
       </c>
@@ -20446,7 +20450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="894" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A894" s="1" t="s">
         <v>56</v>
       </c>
@@ -20464,7 +20468,7 @@
       </c>
       <c r="F894" s="3"/>
     </row>
-    <row r="895" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A895" s="1" t="s">
         <v>56</v>
       </c>
@@ -20482,7 +20486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="896" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A896" s="1" t="s">
         <v>146</v>
       </c>
@@ -20500,7 +20504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="897" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A897" s="1" t="s">
         <v>6</v>
       </c>
@@ -20518,7 +20522,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="898" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A898" s="1" t="s">
         <v>172</v>
       </c>
@@ -20536,7 +20540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="899" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A899" s="1" t="s">
         <v>505</v>
       </c>
@@ -20556,7 +20560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="900" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A900" s="1" t="s">
         <v>222</v>
       </c>
@@ -20576,7 +20580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="901" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A901" s="1" t="s">
         <v>6</v>
       </c>
@@ -20596,7 +20600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="902" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A902" s="1" t="s">
         <v>111</v>
       </c>
@@ -20616,7 +20620,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="903" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A903" s="1" t="s">
         <v>712</v>
       </c>
@@ -20636,7 +20640,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="904" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A904" s="1" t="s">
         <v>712</v>
       </c>
@@ -20656,7 +20660,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="905" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A905" s="1" t="s">
         <v>6</v>
       </c>
@@ -20676,7 +20680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="906" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A906" s="1" t="s">
         <v>6</v>
       </c>
@@ -20696,7 +20700,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="907" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A907" s="1" t="s">
         <v>263</v>
       </c>
@@ -20716,7 +20720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="908" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A908" s="1" t="s">
         <v>56</v>
       </c>
@@ -20736,7 +20740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="909" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A909" s="1" t="s">
         <v>56</v>
       </c>
@@ -20756,7 +20760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="910" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A910" s="1" t="s">
         <v>146</v>
       </c>
@@ -20776,7 +20780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="911" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A911" s="1" t="s">
         <v>172</v>
       </c>
@@ -20796,7 +20800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="912" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A912" s="1" t="s">
         <v>222</v>
       </c>
@@ -20816,7 +20820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="913" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A913" s="1" t="s">
         <v>6</v>
       </c>
@@ -20836,7 +20840,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="914" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A914" s="1" t="s">
         <v>6</v>
       </c>
@@ -20856,7 +20860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="915" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A915" s="1" t="s">
         <v>222</v>
       </c>
@@ -20876,7 +20880,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="916" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A916" s="1" t="s">
         <v>172</v>
       </c>
@@ -20896,7 +20900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="917" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A917" s="1" t="s">
         <v>6</v>
       </c>
@@ -20916,7 +20920,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="918" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A918" s="1" t="s">
         <v>146</v>
       </c>
@@ -20936,7 +20940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="919" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A919" s="1" t="s">
         <v>56</v>
       </c>
@@ -20956,7 +20960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="920" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A920" s="1" t="s">
         <v>56</v>
       </c>
@@ -20976,7 +20980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="921" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A921" s="1" t="s">
         <v>263</v>
       </c>
@@ -20996,7 +21000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="922" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A922" s="1" t="s">
         <v>56</v>
       </c>
@@ -21016,7 +21020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="923" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A923" s="1" t="s">
         <v>146</v>
       </c>
@@ -21036,7 +21040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="924" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A924" s="1" t="s">
         <v>6</v>
       </c>
@@ -21056,7 +21060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="925" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A925" s="1" t="s">
         <v>146</v>
       </c>
@@ -21076,7 +21080,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="926" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A926" s="1" t="s">
         <v>111</v>
       </c>
@@ -21094,7 +21098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="927" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A927" s="1" t="s">
         <v>263</v>
       </c>
@@ -21112,7 +21116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="928" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A928" s="1" t="s">
         <v>146</v>
       </c>
@@ -21130,7 +21134,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="929" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A929" s="1" t="s">
         <v>505</v>
       </c>
@@ -21148,7 +21152,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="930" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A930" s="1" t="s">
         <v>505</v>
       </c>
@@ -21166,7 +21170,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="931" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A931" s="1" t="s">
         <v>111</v>
       </c>
@@ -21186,7 +21190,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="932" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A932" s="1" t="s">
         <v>146</v>
       </c>
@@ -21206,7 +21210,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="933" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A933" s="1" t="s">
         <v>222</v>
       </c>
@@ -21226,7 +21230,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="934" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A934" s="1" t="s">
         <v>146</v>
       </c>
@@ -21246,7 +21250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="935" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A935" s="1" t="s">
         <v>6</v>
       </c>
@@ -21266,7 +21270,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="936" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A936" s="1" t="s">
         <v>505</v>
       </c>
@@ -21286,7 +21290,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="937" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A937" s="1" t="s">
         <v>172</v>
       </c>
@@ -21306,7 +21310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="938" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A938" s="1" t="s">
         <v>6</v>
       </c>
@@ -21326,7 +21330,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="939" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A939" s="1" t="s">
         <v>222</v>
       </c>
@@ -21344,7 +21348,7 @@
       </c>
       <c r="F939" s="3"/>
     </row>
-    <row r="940" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A940" s="1" t="s">
         <v>6</v>
       </c>
@@ -21362,7 +21366,7 @@
       </c>
       <c r="F940" s="3"/>
     </row>
-    <row r="941" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A941" s="1" t="s">
         <v>111</v>
       </c>
@@ -21382,7 +21386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="942" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A942" s="1" t="s">
         <v>56</v>
       </c>
@@ -21402,7 +21406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="943" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A943" s="1" t="s">
         <v>6</v>
       </c>
@@ -21422,7 +21426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="944" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A944" s="1" t="s">
         <v>146</v>
       </c>
@@ -21442,7 +21446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="945" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A945" s="1" t="s">
         <v>56</v>
       </c>
@@ -21462,7 +21466,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="946" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A946" s="1" t="s">
         <v>146</v>
       </c>
@@ -21482,7 +21486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="947" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A947" s="1" t="s">
         <v>505</v>
       </c>
@@ -21502,7 +21506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="948" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A948" s="1" t="s">
         <v>505</v>
       </c>
@@ -21520,7 +21524,7 @@
       </c>
       <c r="F948" s="3"/>
     </row>
-    <row r="949" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A949" s="1" t="s">
         <v>505</v>
       </c>
@@ -21540,7 +21544,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="950" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A950" s="1" t="s">
         <v>56</v>
       </c>
@@ -21560,7 +21564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="951" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A951" s="1" t="s">
         <v>222</v>
       </c>
@@ -21580,7 +21584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="952" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A952" s="1" t="s">
         <v>712</v>
       </c>
@@ -21600,7 +21604,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="953" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A953" s="1" t="s">
         <v>222</v>
       </c>
@@ -21620,7 +21624,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="954" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A954" s="1" t="s">
         <v>146</v>
       </c>
@@ -21640,7 +21644,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="955" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A955" s="1" t="s">
         <v>146</v>
       </c>
@@ -21660,7 +21664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="956" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A956" s="1" t="s">
         <v>6</v>
       </c>
@@ -21700,7 +21704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="958" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A958" s="1" t="s">
         <v>222</v>
       </c>
@@ -21720,7 +21724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="959" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A959" s="1" t="s">
         <v>146</v>
       </c>
@@ -21740,7 +21744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="960" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A960" s="1" t="s">
         <v>111</v>
       </c>
@@ -21760,7 +21764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="961" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A961" s="1" t="s">
         <v>146</v>
       </c>
@@ -21780,7 +21784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="962" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A962" s="1" t="s">
         <v>6</v>
       </c>
@@ -21798,7 +21802,7 @@
       </c>
       <c r="F962" s="3"/>
     </row>
-    <row r="963" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A963" s="1" t="s">
         <v>222</v>
       </c>
@@ -21816,7 +21820,7 @@
       </c>
       <c r="F963" s="3"/>
     </row>
-    <row r="964" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A964" s="1" t="s">
         <v>111</v>
       </c>
@@ -21836,7 +21840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="965" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A965" s="1" t="s">
         <v>172</v>
       </c>
@@ -21856,7 +21860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="966" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A966" s="1" t="s">
         <v>146</v>
       </c>
@@ -21876,7 +21880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="967" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A967" s="1" t="s">
         <v>222</v>
       </c>
@@ -21896,7 +21900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="968" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A968" s="1" t="s">
         <v>172</v>
       </c>
@@ -21916,7 +21920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="969" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A969" s="1" t="s">
         <v>6</v>
       </c>
@@ -21936,7 +21940,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="970" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A970" s="1" t="s">
         <v>56</v>
       </c>
@@ -21956,7 +21960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="971" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A971" s="1" t="s">
         <v>172</v>
       </c>
@@ -21974,7 +21978,7 @@
       </c>
       <c r="F971" s="3"/>
     </row>
-    <row r="972" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A972" s="1" t="s">
         <v>505</v>
       </c>
@@ -21994,7 +21998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="973" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A973" s="1" t="s">
         <v>505</v>
       </c>
@@ -22014,7 +22018,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="974" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A974" s="1" t="s">
         <v>222</v>
       </c>
@@ -22034,7 +22038,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="975" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A975" s="1" t="s">
         <v>172</v>
       </c>
@@ -22054,7 +22058,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="976" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A976" s="1" t="s">
         <v>222</v>
       </c>
@@ -22074,7 +22078,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="977" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A977" s="1" t="s">
         <v>146</v>
       </c>
@@ -22094,7 +22098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="978" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A978" s="1" t="s">
         <v>146</v>
       </c>
@@ -22114,7 +22118,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="979" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A979" s="1" t="s">
         <v>111</v>
       </c>
@@ -22132,7 +22136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="980" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A980" s="1" t="s">
         <v>146</v>
       </c>
@@ -22150,7 +22154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="981" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A981" s="1" t="s">
         <v>505</v>
       </c>
@@ -22170,7 +22174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="982" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A982" s="1" t="s">
         <v>222</v>
       </c>
@@ -22190,7 +22194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="983" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A983" s="1" t="s">
         <v>146</v>
       </c>
@@ -22210,7 +22214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="984" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A984" s="1" t="s">
         <v>146</v>
       </c>
@@ -22228,7 +22232,7 @@
       </c>
       <c r="F984" s="3"/>
     </row>
-    <row r="985" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A985" s="1" t="s">
         <v>222</v>
       </c>
@@ -22248,7 +22252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="986" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A986" s="1" t="s">
         <v>172</v>
       </c>
@@ -22268,7 +22272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="987" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A987" s="1" t="s">
         <v>111</v>
       </c>
@@ -22288,7 +22292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="988" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A988" s="1" t="s">
         <v>56</v>
       </c>
@@ -22308,7 +22312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="989" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A989" s="1" t="s">
         <v>146</v>
       </c>
@@ -22328,7 +22332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="990" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A990" s="1" t="s">
         <v>146</v>
       </c>
@@ -22348,7 +22352,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="991" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A991" s="1" t="s">
         <v>172</v>
       </c>
@@ -22368,7 +22372,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="992" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A992" s="1" t="s">
         <v>111</v>
       </c>
@@ -22388,7 +22392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="993" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A993" s="1" t="s">
         <v>56</v>
       </c>
@@ -22408,7 +22412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="994" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A994" s="1" t="s">
         <v>222</v>
       </c>
@@ -22428,7 +22432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="995" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A995" s="1" t="s">
         <v>172</v>
       </c>
@@ -22448,7 +22452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="996" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A996" s="1" t="s">
         <v>111</v>
       </c>
@@ -22468,7 +22472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="997" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A997" s="1" t="s">
         <v>111</v>
       </c>
@@ -22488,7 +22492,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="998" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A998" s="1" t="s">
         <v>6</v>
       </c>
@@ -22508,7 +22512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="999" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A999" s="1" t="s">
         <v>146</v>
       </c>
@@ -22528,7 +22532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1000" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="1" t="s">
         <v>6</v>
       </c>
@@ -22548,7 +22552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1001" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="1" t="s">
         <v>146</v>
       </c>
@@ -22566,7 +22570,7 @@
       </c>
       <c r="F1001" s="3"/>
     </row>
-    <row r="1002" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="1" t="s">
         <v>56</v>
       </c>
@@ -22586,7 +22590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1003" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="1" t="s">
         <v>111</v>
       </c>
@@ -22606,7 +22610,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1004" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="1" t="s">
         <v>263</v>
       </c>
@@ -22626,7 +22630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1005" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="1" t="s">
         <v>56</v>
       </c>
@@ -22646,7 +22650,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1006" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="1" t="s">
         <v>146</v>
       </c>
@@ -22666,7 +22670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1007" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="1" t="s">
         <v>172</v>
       </c>
@@ -22686,7 +22690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1008" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="1" t="s">
         <v>222</v>
       </c>
@@ -22706,7 +22710,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1009" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="1" t="s">
         <v>172</v>
       </c>
@@ -22726,7 +22730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1010" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="1" t="s">
         <v>505</v>
       </c>
@@ -22744,7 +22748,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1011" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="1" t="s">
         <v>263</v>
       </c>
@@ -22762,7 +22766,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1012" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="1" t="s">
         <v>56</v>
       </c>
@@ -22782,7 +22786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1013" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="1" t="s">
         <v>6</v>
       </c>
@@ -22802,7 +22806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1014" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="1" t="s">
         <v>505</v>
       </c>
@@ -22820,7 +22824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1015" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="1" t="s">
         <v>263</v>
       </c>
@@ -22840,7 +22844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1016" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1016" s="1" t="s">
         <v>56</v>
       </c>
@@ -22860,7 +22864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1017" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="1" t="s">
         <v>146</v>
       </c>
@@ -22880,7 +22884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1018" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1018" s="1" t="s">
         <v>56</v>
       </c>
@@ -22900,7 +22904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1019" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1019" s="1" t="s">
         <v>172</v>
       </c>
@@ -22918,7 +22922,7 @@
       </c>
       <c r="F1019" s="3"/>
     </row>
-    <row r="1020" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1020" s="1" t="s">
         <v>56</v>
       </c>
@@ -22938,7 +22942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1021" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1021" s="1" t="s">
         <v>111</v>
       </c>
@@ -22958,7 +22962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1022" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1022" s="1" t="s">
         <v>505</v>
       </c>
@@ -22978,7 +22982,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="1023" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1023" s="1" t="s">
         <v>222</v>
       </c>
@@ -22998,7 +23002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1024" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1024" s="1" t="s">
         <v>505</v>
       </c>
@@ -23018,7 +23022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1025" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1025" s="1" t="s">
         <v>263</v>
       </c>
@@ -23038,7 +23042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1026" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1026" s="1" t="s">
         <v>172</v>
       </c>
@@ -23058,7 +23062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1027" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1027" s="1" t="s">
         <v>146</v>
       </c>
@@ -23076,7 +23080,7 @@
       </c>
       <c r="F1027" s="3"/>
     </row>
-    <row r="1028" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1028" s="1" t="s">
         <v>712</v>
       </c>
@@ -23096,7 +23100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1029" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1029" s="1" t="s">
         <v>146</v>
       </c>
@@ -23116,7 +23120,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1030" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1030" s="1" t="s">
         <v>146</v>
       </c>
@@ -23136,7 +23140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1031" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1031" s="1" t="s">
         <v>146</v>
       </c>
@@ -23156,7 +23160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1032" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1032" s="1" t="s">
         <v>6</v>
       </c>
@@ -23176,7 +23180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1033" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1033" s="1" t="s">
         <v>222</v>
       </c>
@@ -23194,7 +23198,7 @@
       </c>
       <c r="F1033" s="3"/>
     </row>
-    <row r="1034" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1034" s="1" t="s">
         <v>56</v>
       </c>
@@ -23214,7 +23218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1035" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="1" t="s">
         <v>222</v>
       </c>
@@ -23234,7 +23238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1036" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1036" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="1" t="s">
         <v>146</v>
       </c>
@@ -23254,7 +23258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1037" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1037" s="1" t="s">
         <v>111</v>
       </c>
@@ -23274,7 +23278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1038" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1038" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1038" s="1" t="s">
         <v>505</v>
       </c>
@@ -23292,7 +23296,7 @@
       </c>
       <c r="F1038" s="3"/>
     </row>
-    <row r="1039" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1039" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1039" s="1" t="s">
         <v>146</v>
       </c>
@@ -23312,7 +23316,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="1040" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1040" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1040" s="1" t="s">
         <v>111</v>
       </c>
@@ -23330,7 +23334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1041" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1041" s="1" t="s">
         <v>712</v>
       </c>
@@ -23348,7 +23352,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1042" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1042" s="1" t="s">
         <v>146</v>
       </c>
@@ -23366,7 +23370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1043" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1043" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1043" s="1" t="s">
         <v>172</v>
       </c>
@@ -23386,7 +23390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1044" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1044" s="1" t="s">
         <v>146</v>
       </c>
@@ -23406,7 +23410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1045" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1045" s="1" t="s">
         <v>6</v>
       </c>
@@ -23426,7 +23430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1046" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1046" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1046" s="1" t="s">
         <v>263</v>
       </c>
@@ -23446,7 +23450,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="1047" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1047" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="1" t="s">
         <v>146</v>
       </c>
@@ -23466,7 +23470,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="1048" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1048" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1048" s="1" t="s">
         <v>146</v>
       </c>
@@ -23486,7 +23490,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="1049" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1049" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1049" s="1" t="s">
         <v>146</v>
       </c>
@@ -23506,7 +23510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1050" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1050" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1050" s="1" t="s">
         <v>172</v>
       </c>
@@ -23526,7 +23530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1051" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1051" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1051" s="1" t="s">
         <v>172</v>
       </c>
@@ -23546,7 +23550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1052" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1052" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="1" t="s">
         <v>222</v>
       </c>
@@ -23566,7 +23570,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="1053" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1053" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1053" s="1" t="s">
         <v>146</v>
       </c>
@@ -23606,7 +23610,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1055" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1055" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1055" s="1" t="s">
         <v>505</v>
       </c>
@@ -23624,7 +23628,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1056" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1056" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1056" s="1" t="s">
         <v>263</v>
       </c>
@@ -23642,7 +23646,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1057" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1057" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1057" s="1" t="s">
         <v>56</v>
       </c>
@@ -23660,7 +23664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1058" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1058" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="1" t="s">
         <v>172</v>
       </c>
@@ -23678,7 +23682,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1059" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1059" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1059" s="1" t="s">
         <v>712</v>
       </c>
@@ -23698,7 +23702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1060" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1060" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="1" t="s">
         <v>263</v>
       </c>
@@ -23718,7 +23722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1061" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1061" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1061" s="1" t="s">
         <v>146</v>
       </c>
@@ -23738,7 +23742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1062" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1062" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1062" s="1" t="s">
         <v>111</v>
       </c>
@@ -23778,7 +23782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1064" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1064" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1064" s="1" t="s">
         <v>712</v>
       </c>
@@ -23798,7 +23802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1065" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1065" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1065" s="1" t="s">
         <v>6</v>
       </c>
@@ -23818,7 +23822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1066" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1066" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1066" s="1" t="s">
         <v>56</v>
       </c>
@@ -23838,7 +23842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1067" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1067" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1067" s="1" t="s">
         <v>505</v>
       </c>
@@ -23858,7 +23862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1068" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1068" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1068" s="1" t="s">
         <v>222</v>
       </c>
@@ -23874,7 +23878,7 @@
       <c r="E1068" s="3"/>
       <c r="F1068" s="3"/>
     </row>
-    <row r="1069" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1069" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1069" s="1" t="s">
         <v>6</v>
       </c>
@@ -23914,7 +23918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1071" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1071" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="1" t="s">
         <v>6</v>
       </c>
@@ -23934,7 +23938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1072" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1072" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="1" t="s">
         <v>56</v>
       </c>
@@ -23954,7 +23958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1073" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1073" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="1" t="s">
         <v>6</v>
       </c>
@@ -23974,7 +23978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1074" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1074" s="1" t="s">
         <v>172</v>
       </c>
@@ -24014,7 +24018,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="1076" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1076" s="1" t="s">
         <v>222</v>
       </c>
@@ -24034,7 +24038,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="1077" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1077" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="1" t="s">
         <v>172</v>
       </c>
@@ -24054,7 +24058,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="1078" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1078" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="1" t="s">
         <v>222</v>
       </c>
@@ -24074,7 +24078,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1079" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="1" t="s">
         <v>712</v>
       </c>
@@ -24094,7 +24098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1080" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1080" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="1" t="s">
         <v>146</v>
       </c>
@@ -24114,7 +24118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1081" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1081" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1081" s="1" t="s">
         <v>222</v>
       </c>
@@ -24134,7 +24138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1082" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1082" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1082" s="1" t="s">
         <v>146</v>
       </c>
@@ -24154,7 +24158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1083" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1083" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1083" s="1" t="s">
         <v>172</v>
       </c>
@@ -24174,7 +24178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1084" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1084" spans="1:6" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1084" s="1" t="s">
         <v>172</v>
       </c>
@@ -24194,7 +24198,34 @@
         <v>25</v>
       </c>
     </row>
+    <row r="1085" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1085" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1085" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C1085" s="2">
+        <v>481875</v>
+      </c>
+      <c r="D1085" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1085" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1085" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F1084" xr:uid="{FC219B49-20BB-ED4C-B167-301B561CF408}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="LSG"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>